--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N87_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N87_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.56311637566609</v>
+        <v>6.42900641104574</v>
       </c>
       <c r="D2" t="n">
-        <v>41.69495167814111</v>
+        <v>6.775429647697931</v>
       </c>
       <c r="E2" t="n">
-        <v>16.0864647293265</v>
+        <v>2.614050518515557</v>
       </c>
       <c r="F2" t="n">
-        <v>16.12155162957187</v>
+        <v>2.619752139805429</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>61.10240622895813</v>
+        <v>9.929141012205697</v>
       </c>
       <c r="D3" t="n">
-        <v>62.95859213032639</v>
+        <v>10.23077122117804</v>
       </c>
       <c r="E3" t="n">
-        <v>16.0864647293265</v>
+        <v>2.614050518515557</v>
       </c>
       <c r="F3" t="n">
-        <v>16.12155162957187</v>
+        <v>2.619752139805429</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>65.50932293934355</v>
+        <v>10.64526497764333</v>
       </c>
       <c r="D4" t="n">
-        <v>66.42278759707347</v>
+        <v>10.79370298452444</v>
       </c>
       <c r="E4" t="n">
-        <v>16.0864647293265</v>
+        <v>2.614050518515557</v>
       </c>
       <c r="F4" t="n">
-        <v>16.12155162957187</v>
+        <v>2.619752139805429</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>61.25315377360744</v>
+        <v>9.953637488211211</v>
       </c>
       <c r="D5" t="n">
-        <v>61.90908994064938</v>
+        <v>10.06022711535553</v>
       </c>
       <c r="E5" t="n">
-        <v>16.0864647293265</v>
+        <v>2.614050518515557</v>
       </c>
       <c r="F5" t="n">
-        <v>16.12155162957187</v>
+        <v>2.619752139805429</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.07807738913244</v>
+        <v>4.400187575734021</v>
       </c>
       <c r="D6" t="n">
-        <v>27.96532293168756</v>
+        <v>4.544364976399229</v>
       </c>
       <c r="E6" t="n">
-        <v>16.0864647293265</v>
+        <v>2.614050518515557</v>
       </c>
       <c r="F6" t="n">
-        <v>16.12155162957187</v>
+        <v>2.619752139805429</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.5086259685462</v>
+        <v>6.582651719888758</v>
       </c>
       <c r="D7" t="n">
-        <v>40.66501573442066</v>
+        <v>6.608065056843358</v>
       </c>
       <c r="E7" t="n">
-        <v>16.0864647293265</v>
+        <v>2.614050518515557</v>
       </c>
       <c r="F7" t="n">
-        <v>16.12155162957187</v>
+        <v>2.619752139805429</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>43.34338962523624</v>
+        <v>7.043300814100889</v>
       </c>
       <c r="D8" t="n">
-        <v>44.60798768882799</v>
+        <v>7.248797999434548</v>
       </c>
       <c r="E8" t="n">
-        <v>16.0864647293265</v>
+        <v>2.614050518515557</v>
       </c>
       <c r="F8" t="n">
-        <v>16.12155162957187</v>
+        <v>2.619752139805429</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>13.46111671805762</v>
+        <v>2.187431466684363</v>
       </c>
       <c r="D9" t="n">
-        <v>14.71089687238885</v>
+        <v>2.390520741763189</v>
       </c>
       <c r="E9" t="n">
-        <v>16.0864647293265</v>
+        <v>2.614050518515557</v>
       </c>
       <c r="F9" t="n">
-        <v>16.12155162957187</v>
+        <v>2.619752139805429</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>45.63721638128087</v>
+        <v>7.416047661958141</v>
       </c>
       <c r="D10" t="n">
-        <v>46.69533551318382</v>
+        <v>7.587992020892371</v>
       </c>
       <c r="E10" t="n">
-        <v>16.0864647293265</v>
+        <v>2.614050518515557</v>
       </c>
       <c r="F10" t="n">
-        <v>16.12155162957187</v>
+        <v>2.619752139805429</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>35.73096235614809</v>
+        <v>5.806281382874065</v>
       </c>
       <c r="D11" t="n">
-        <v>36.26181933540811</v>
+        <v>5.892545642003817</v>
       </c>
       <c r="E11" t="n">
-        <v>16.0864647293265</v>
+        <v>2.614050518515557</v>
       </c>
       <c r="F11" t="n">
-        <v>16.12155162957187</v>
+        <v>2.619752139805429</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>24.44686605152106</v>
+        <v>3.972615733372172</v>
       </c>
       <c r="D12" t="n">
-        <v>24.40049242982871</v>
+        <v>3.965080019847165</v>
       </c>
       <c r="E12" t="n">
-        <v>16.0864647293265</v>
+        <v>2.614050518515557</v>
       </c>
       <c r="F12" t="n">
-        <v>16.12155162957187</v>
+        <v>2.619752139805429</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>62.77794826559425</v>
+        <v>10.20141659315907</v>
       </c>
       <c r="D13" t="n">
-        <v>62.80572769136282</v>
+        <v>10.20593074984646</v>
       </c>
       <c r="E13" t="n">
-        <v>16.0864647293265</v>
+        <v>2.614050518515557</v>
       </c>
       <c r="F13" t="n">
-        <v>16.12155162957187</v>
+        <v>2.619752139805429</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
